--- a/artfynd/A 34737-2024 artfynd.xlsx
+++ b/artfynd/A 34737-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>119796671</v>
       </c>
       <c r="B3" t="n">
-        <v>97824</v>
+        <v>97847</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 34737-2024 artfynd.xlsx
+++ b/artfynd/A 34737-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>16887936</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>796563.1909966322</v>
+        <v>796563</v>
       </c>
       <c r="R2" t="n">
-        <v>7350367.14161985</v>
+        <v>7350367</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2014-10-21</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2014-10-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -792,54 +777,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119796671</v>
+        <v>16888917</v>
       </c>
       <c r="B3" t="n">
-        <v>97847</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Åträsk, Nb</t>
+          <t>1900 m N Åträsk, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>796490</v>
+        <v>796355</v>
       </c>
       <c r="R3" t="n">
-        <v>7350360</v>
+        <v>7350371</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,17 +842,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2014-10-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2014-10-17</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>Sveaskog naturvärdesinventering, inventerare: Mats Bergkvist</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,15 +867,223 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Sveaskog genom Johan Ekenstedt</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>16888918</v>
+      </c>
+      <c r="B4" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>1900 m N Åträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>796346</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7350381</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2014-10-17</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2014-10-17</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Sveaskog naturvärdesinventering, inventerare: Mats Bergkvist</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Sveaskog genom Johan Ekenstedt</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>119796671</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Åträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>796490</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7350360</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-08-19</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-08-19</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Mimmi Persson</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Mimmi Persson</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34737-2024 artfynd.xlsx
+++ b/artfynd/A 34737-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16887936</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16888917</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16888918</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1084,8 +1104,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119796671</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>